--- a/PhD_Timeline_ANU.xlsx
+++ b/PhD_Timeline_ANU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u8363323_anu_edu_au/Documents/Doctoral Documents/QTimeline/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u8363323_anu_edu_au/Documents/Doctoral Documents/PhD-Timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E98A0C4-0D5F-4AAB-BDC4-85E8952CE09A}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214E82F8-DF49-4C8A-932D-7CDA22BE6C64}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,7 +747,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode=";;;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1205,6 +1205,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1385,29 +1389,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K58"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="62.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.15234375" customWidth="1"/>
+    <col min="3" max="3" width="62.84375" customWidth="1"/>
+    <col min="4" max="4" width="11.3828125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="97.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="97.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.100000000000001">
+    <row r="1" spans="1:11" ht="20.149999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
@@ -1424,7 +1428,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="24" t="s">
         <v>2</v>
       </c>
@@ -1442,7 +1446,7 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="24" t="s">
         <v>3</v>
       </c>
@@ -1460,7 +1464,7 @@
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
         <v>4</v>
       </c>
@@ -1478,7 +1482,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="22" t="s">
         <v>5</v>
       </c>
@@ -1496,7 +1500,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
@@ -1514,7 +1518,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="24" t="s">
         <v>7</v>
       </c>
@@ -1532,7 +1536,7 @@
       <c r="J9" s="23"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="24" t="s">
         <v>8</v>
       </c>
@@ -1550,7 +1554,7 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
         <v>9</v>
       </c>
@@ -1558,7 +1562,7 @@
       <c r="C11" s="23"/>
       <c r="D11" s="27">
         <f>COUNTIF(J14:J57,"Done")/COUNTA(A14:A57)</f>
-        <v>2.2727272727272728E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
@@ -1568,7 +1572,7 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -1581,7 +1585,7 @@
       <c r="J12" s="23"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" spans="1:11" ht="27.75" customHeight="1">
+    <row r="13" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="28" t="s">
         <v>10</v>
       </c>
@@ -1616,7 +1620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="29" t="s">
         <v>21</v>
       </c>
@@ -1653,7 +1657,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
         <v>27</v>
       </c>
@@ -1688,7 +1692,7 @@
       </c>
       <c r="K15" s="30"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="29" t="s">
         <v>29</v>
       </c>
@@ -1719,11 +1723,11 @@
         <v>24</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K16" s="30"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="29" t="s">
         <v>32</v>
       </c>
@@ -1758,7 +1762,7 @@
       </c>
       <c r="K17" s="30"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="29" t="s">
         <v>34</v>
       </c>
@@ -1793,7 +1797,7 @@
       </c>
       <c r="K18" s="30"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1828,7 +1832,7 @@
       </c>
       <c r="K19" s="30"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="29" t="s">
         <v>38</v>
       </c>
@@ -1863,7 +1867,7 @@
       </c>
       <c r="K20" s="30"/>
     </row>
-    <row r="21" spans="1:11" ht="25.7">
+    <row r="21" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A21" s="29" t="s">
         <v>41</v>
       </c>
@@ -1900,7 +1904,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="29" t="s">
         <v>45</v>
       </c>
@@ -1937,7 +1941,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="29" t="s">
         <v>48</v>
       </c>
@@ -1974,7 +1978,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
         <v>52</v>
       </c>
@@ -2011,7 +2015,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="29" t="s">
         <v>56</v>
       </c>
@@ -2048,7 +2052,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="29" t="s">
         <v>60</v>
       </c>
@@ -2085,7 +2089,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="29" t="s">
         <v>63</v>
       </c>
@@ -2120,7 +2124,7 @@
       </c>
       <c r="K27" s="30"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
         <v>65</v>
       </c>
@@ -2157,7 +2161,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
         <v>68</v>
       </c>
@@ -2194,7 +2198,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="25.7">
+    <row r="30" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A30" s="29" t="s">
         <v>72</v>
       </c>
@@ -2231,7 +2235,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="25.7">
+    <row r="31" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>75</v>
       </c>
@@ -2268,7 +2272,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
         <v>78</v>
       </c>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="K32" s="30"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="29" t="s">
         <v>81</v>
       </c>
@@ -2340,7 +2344,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="29" t="s">
         <v>84</v>
       </c>
@@ -2377,7 +2381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="29" t="s">
         <v>87</v>
       </c>
@@ -2414,7 +2418,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="29" t="s">
         <v>91</v>
       </c>
@@ -2451,7 +2455,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="29" t="s">
         <v>94</v>
       </c>
@@ -2488,7 +2492,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="29" t="s">
         <v>99</v>
       </c>
@@ -2523,7 +2527,7 @@
       </c>
       <c r="K38" s="30"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
         <v>101</v>
       </c>
@@ -2560,7 +2564,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
         <v>104</v>
       </c>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="K40" s="30"/>
     </row>
-    <row r="41" spans="1:11" ht="25.7">
+    <row r="41" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
         <v>106</v>
       </c>
@@ -2632,7 +2636,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="29" t="s">
         <v>109</v>
       </c>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="K42" s="30"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="29" t="s">
         <v>111</v>
       </c>
@@ -2704,7 +2708,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="29" t="s">
         <v>114</v>
       </c>
@@ -2739,7 +2743,7 @@
       </c>
       <c r="K44" s="30"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="29" t="s">
         <v>117</v>
       </c>
@@ -2774,7 +2778,7 @@
       </c>
       <c r="K45" s="30"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="29" t="s">
         <v>119</v>
       </c>
@@ -2809,7 +2813,7 @@
       </c>
       <c r="K46" s="30"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="29" t="s">
         <v>121</v>
       </c>
@@ -2844,7 +2848,7 @@
       </c>
       <c r="K47" s="30"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="29" t="s">
         <v>123</v>
       </c>
@@ -2881,7 +2885,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="29" t="s">
         <v>126</v>
       </c>
@@ -2918,7 +2922,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="29" t="s">
         <v>129</v>
       </c>
@@ -2953,7 +2957,7 @@
       </c>
       <c r="K50" s="30"/>
     </row>
-    <row r="51" spans="1:11" ht="25.7">
+    <row r="51" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A51" s="29" t="s">
         <v>131</v>
       </c>
@@ -2990,7 +2994,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="29" t="s">
         <v>134</v>
       </c>
@@ -3027,7 +3031,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="29" t="s">
         <v>136</v>
       </c>
@@ -3062,7 +3066,7 @@
       </c>
       <c r="K53" s="30"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="29" t="s">
         <v>138</v>
       </c>
@@ -3097,7 +3101,7 @@
       </c>
       <c r="K54" s="30"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="29" t="s">
         <v>140</v>
       </c>
@@ -3134,7 +3138,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="25.7">
+    <row r="56" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A56" s="29" t="s">
         <v>143</v>
       </c>
@@ -3171,7 +3175,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="29" t="s">
         <v>148</v>
       </c>
@@ -3208,7 +3212,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" s="23"/>
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
@@ -3267,22 +3271,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AV49"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="6" width="8" customWidth="1"/>
-    <col min="7" max="48" width="3.5703125" customWidth="1"/>
+    <col min="7" max="48" width="3.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="17.649999999999999">
+    <row r="1" spans="1:48" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:48">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.4">
       <c r="G3" s="7" t="s">
         <v>153</v>
       </c>
@@ -3334,7 +3338,7 @@
       <c r="AU3" s="14"/>
       <c r="AV3" s="14"/>
     </row>
-    <row r="4" spans="1:48">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
         <v>10</v>
       </c>
@@ -3480,7 +3484,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:48" ht="42" customHeight="1">
+    <row r="5" spans="1:48" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -3656,7 +3660,7 @@
         <v>Feb 30</v>
       </c>
     </row>
-    <row r="6" spans="1:48">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="str">
         <f>Timeline!A14</f>
         <v>T01</v>
@@ -3850,7 +3854,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:48">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="str">
         <f>Timeline!A15</f>
         <v>T02</v>
@@ -4044,7 +4048,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:48">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="str">
         <f>Timeline!A16</f>
         <v>T03</v>
@@ -4238,7 +4242,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:48">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="str">
         <f>Timeline!A17</f>
         <v>T04</v>
@@ -4432,7 +4436,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:48">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="str">
         <f>Timeline!A18</f>
         <v>T05</v>
@@ -4626,7 +4630,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:48">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="str">
         <f>Timeline!A19</f>
         <v>T06</v>
@@ -4820,7 +4824,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:48">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="str">
         <f>Timeline!A20</f>
         <v>T07</v>
@@ -5014,7 +5018,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:48">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="str">
         <f>Timeline!A21</f>
         <v>T08</v>
@@ -5208,7 +5212,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:48">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="str">
         <f>Timeline!A22</f>
         <v>T09</v>
@@ -5402,7 +5406,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:48">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="str">
         <f>Timeline!A23</f>
         <v>T10</v>
@@ -5596,7 +5600,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:48">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="str">
         <f>Timeline!A24</f>
         <v>T11</v>
@@ -5790,7 +5794,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:48">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="str">
         <f>Timeline!A25</f>
         <v>T12</v>
@@ -5984,7 +5988,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:48">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="str">
         <f>Timeline!A26</f>
         <v>T13</v>
@@ -6178,7 +6182,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:48">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="str">
         <f>Timeline!A27</f>
         <v>T14</v>
@@ -6372,7 +6376,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:48">
+    <row r="20" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="str">
         <f>Timeline!A28</f>
         <v>T15</v>
@@ -6566,7 +6570,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:48">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="str">
         <f>Timeline!A29</f>
         <v>T16</v>
@@ -6760,7 +6764,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:48">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="str">
         <f>Timeline!A30</f>
         <v>T17</v>
@@ -6954,7 +6958,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:48">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="str">
         <f>Timeline!A31</f>
         <v>T18</v>
@@ -7148,7 +7152,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:48">
+    <row r="24" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="str">
         <f>Timeline!A32</f>
         <v>T19</v>
@@ -7342,7 +7346,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:48">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="str">
         <f>Timeline!A33</f>
         <v>T20</v>
@@ -7536,7 +7540,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:48">
+    <row r="26" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="str">
         <f>Timeline!A34</f>
         <v>T21</v>
@@ -7730,7 +7734,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:48">
+    <row r="27" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="str">
         <f>Timeline!A35</f>
         <v>T22</v>
@@ -7924,7 +7928,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:48">
+    <row r="28" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="str">
         <f>Timeline!A36</f>
         <v>T23</v>
@@ -8118,7 +8122,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:48">
+    <row r="29" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="str">
         <f>Timeline!A37</f>
         <v>T24</v>
@@ -8312,7 +8316,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:48">
+    <row r="30" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="str">
         <f>Timeline!A38</f>
         <v>T25</v>
@@ -8506,7 +8510,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:48">
+    <row r="31" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="str">
         <f>Timeline!A39</f>
         <v>T26</v>
@@ -8700,7 +8704,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:48">
+    <row r="32" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="str">
         <f>Timeline!A40</f>
         <v>T27</v>
@@ -8894,7 +8898,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:48">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="str">
         <f>Timeline!A41</f>
         <v>T28</v>
@@ -9088,7 +9092,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:48">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="str">
         <f>Timeline!A42</f>
         <v>T29</v>
@@ -9282,7 +9286,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:48">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="str">
         <f>Timeline!A43</f>
         <v>T30</v>
@@ -9476,7 +9480,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:48">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="str">
         <f>Timeline!A44</f>
         <v>T31</v>
@@ -9670,7 +9674,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:48">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="str">
         <f>Timeline!A45</f>
         <v>T32</v>
@@ -9864,7 +9868,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:48">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="str">
         <f>Timeline!A46</f>
         <v>T33</v>
@@ -10058,7 +10062,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:48">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="str">
         <f>Timeline!A47</f>
         <v>T34</v>
@@ -10252,7 +10256,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:48">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="str">
         <f>Timeline!A48</f>
         <v>T35</v>
@@ -10446,7 +10450,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:48">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="str">
         <f>Timeline!A49</f>
         <v>T36</v>
@@ -10640,7 +10644,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:48">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="str">
         <f>Timeline!A50</f>
         <v>T37</v>
@@ -10834,7 +10838,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:48">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="str">
         <f>Timeline!A51</f>
         <v>T38</v>
@@ -11028,7 +11032,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:48">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="str">
         <f>Timeline!A52</f>
         <v>T39</v>
@@ -11222,7 +11226,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:48">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="str">
         <f>Timeline!A53</f>
         <v>T40</v>
@@ -11416,7 +11420,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:48">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="str">
         <f>Timeline!A54</f>
         <v>T41</v>
@@ -11610,7 +11614,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:48">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="str">
         <f>Timeline!A55</f>
         <v>T42</v>
@@ -11804,7 +11808,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:48">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="str">
         <f>Timeline!A56</f>
         <v>T43</v>
@@ -11998,7 +12002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:48">
+    <row r="49" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="str">
         <f>Timeline!A57</f>
         <v>T44</v>
@@ -12221,7 +12225,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -12229,12 +12233,12 @@
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.649999999999999">
+    <row r="1" spans="1:4" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
         <v>158</v>
       </c>
@@ -12248,7 +12252,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="37.35">
+    <row r="4" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>162</v>
       </c>
@@ -12262,7 +12266,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="24.95">
+    <row r="5" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>166</v>
       </c>
@@ -12276,7 +12280,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24.95">
+    <row r="6" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>169</v>
       </c>
@@ -12290,7 +12294,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="24.95">
+    <row r="7" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
         <v>173</v>
       </c>
@@ -12304,7 +12308,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="37.35">
+    <row r="8" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>177</v>
       </c>
@@ -12318,7 +12322,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="24.95">
+    <row r="9" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
         <v>181</v>
       </c>
@@ -12332,7 +12336,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="24.95">
+    <row r="10" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
         <v>185</v>
       </c>
@@ -12346,7 +12350,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>189</v>
       </c>
@@ -12360,7 +12364,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.7">
+    <row r="12" spans="1:4" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>193</v>
       </c>
@@ -12374,7 +12378,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="24.95">
+    <row r="13" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
         <v>197</v>
       </c>
@@ -12388,7 +12392,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="24.95">
+    <row r="14" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>201</v>
       </c>
@@ -12402,7 +12406,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="37.35">
+    <row r="15" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
         <v>204</v>
       </c>
@@ -12416,7 +12420,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24.95">
+    <row r="16" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>208</v>
       </c>
@@ -12430,7 +12434,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>212</v>
       </c>
@@ -12444,7 +12448,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="24.95">
+    <row r="18" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>215</v>
       </c>
@@ -12458,7 +12462,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="24.95">
+    <row r="19" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
         <v>218</v>
       </c>
@@ -12472,7 +12476,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="24.95">
+    <row r="20" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
         <v>222</v>
       </c>
@@ -12486,7 +12490,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>225</v>
       </c>
@@ -12500,7 +12504,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="37.35">
+    <row r="22" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
         <v>229</v>
       </c>

--- a/PhD_Timeline_ANU.xlsx
+++ b/PhD_Timeline_ANU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u8363323_anu_edu_au/Documents/Doctoral Documents/PhD-Timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214E82F8-DF49-4C8A-932D-7CDA22BE6C64}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D83AFB-567E-4A2F-A9A9-8A8689857293}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,9 +61,6 @@
     <t>Target Thesis Submission (3 years)</t>
   </si>
   <si>
-    <t>Scholarship program end (3.5 years)</t>
-  </si>
-  <si>
     <t>Maximum Enrolment Period, MEP (4 years)</t>
   </si>
   <si>
@@ -737,6 +734,9 @@
   </si>
   <si>
     <t>4, 29-30</t>
+  </si>
+  <si>
+    <t>Scholarship program end (4 years)</t>
   </si>
 </sst>
 </file>
@@ -1205,10 +1205,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1502,13 +1498,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="24" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="25">
-        <f>EDATE($D$3,42)-1</f>
-        <v>47570</v>
+        <f>EDATE($D$3,48)-1</f>
+        <v>47754</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -1520,7 +1516,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -1538,7 +1534,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -1556,7 +1552,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -1587,51 +1583,51 @@
     </row>
     <row r="13" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="C13" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="D13" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="E13" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="F13" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="G13" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="H13" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="I13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="J13" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="K13" s="28" t="s">
         <v>19</v>
-      </c>
-      <c r="K13" s="28" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="C14" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="30" t="s">
-        <v>23</v>
-      </c>
       <c r="D14" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="33">
         <v>1</v>
@@ -1648,27 +1644,27 @@
         <v>46354</v>
       </c>
       <c r="I14" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="K14" s="30" t="s">
         <v>25</v>
-      </c>
-      <c r="K14" s="30" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>28</v>
-      </c>
       <c r="D15" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="33">
         <v>1</v>
@@ -1685,25 +1681,25 @@
         <v>46354</v>
       </c>
       <c r="I15" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K15" s="30"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>30</v>
-      </c>
       <c r="D16" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="33">
         <v>1</v>
@@ -1720,25 +1716,25 @@
         <v>46354</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>33</v>
-      </c>
       <c r="D17" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="33">
         <v>1</v>
@@ -1755,25 +1751,25 @@
         <v>46354</v>
       </c>
       <c r="I17" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K17" s="30"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>35</v>
-      </c>
       <c r="D18" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="33">
         <v>1</v>
@@ -1790,25 +1786,25 @@
         <v>46384</v>
       </c>
       <c r="I18" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K18" s="30"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>37</v>
-      </c>
       <c r="D19" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="33">
         <v>1</v>
@@ -1825,25 +1821,25 @@
         <v>46354</v>
       </c>
       <c r="I19" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J19" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K19" s="30"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>39</v>
-      </c>
       <c r="D20" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="33">
         <v>1</v>
@@ -1860,62 +1856,62 @@
         <v>46354</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K20" s="30"/>
     </row>
     <row r="21" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A21" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="30" t="s">
+      <c r="D21" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="33">
+        <v>1</v>
+      </c>
+      <c r="F21" s="33">
+        <v>1</v>
+      </c>
+      <c r="G21" s="34">
+        <f t="shared" si="0"/>
+        <v>46294</v>
+      </c>
+      <c r="H21" s="34">
+        <f t="shared" si="1"/>
+        <v>46323</v>
+      </c>
+      <c r="I21" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="33">
-        <v>1</v>
-      </c>
-      <c r="F21" s="33">
-        <v>1</v>
-      </c>
-      <c r="G21" s="34">
-        <f t="shared" si="0"/>
-        <v>46294</v>
-      </c>
-      <c r="H21" s="34">
-        <f t="shared" si="1"/>
-        <v>46323</v>
-      </c>
-      <c r="I21" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21" s="33" t="s">
+      <c r="K21" s="30" t="s">
         <v>43</v>
-      </c>
-      <c r="K21" s="30" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>46</v>
-      </c>
       <c r="D22" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="33">
         <v>1</v>
@@ -1932,64 +1928,64 @@
         <v>46354</v>
       </c>
       <c r="I22" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K22" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="30" t="s">
+      <c r="D23" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="33">
+        <v>1</v>
+      </c>
+      <c r="F23" s="33">
+        <v>1</v>
+      </c>
+      <c r="G23" s="34">
+        <f t="shared" si="0"/>
+        <v>46294</v>
+      </c>
+      <c r="H23" s="34">
+        <f t="shared" si="1"/>
+        <v>46323</v>
+      </c>
+      <c r="I23" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="33">
-        <v>1</v>
-      </c>
-      <c r="F23" s="33">
-        <v>1</v>
-      </c>
-      <c r="G23" s="34">
-        <f t="shared" si="0"/>
-        <v>46294</v>
-      </c>
-      <c r="H23" s="34">
-        <f t="shared" si="1"/>
-        <v>46323</v>
-      </c>
-      <c r="I23" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="33" t="s">
+      <c r="K23" s="30" t="s">
         <v>50</v>
-      </c>
-      <c r="K23" s="30" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="31" t="s">
+      <c r="D24" s="32" t="s">
         <v>53</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>54</v>
       </c>
       <c r="E24" s="33">
         <v>3</v>
@@ -2006,27 +2002,27 @@
         <v>46384</v>
       </c>
       <c r="I24" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="C25" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="30" t="s">
-        <v>58</v>
-      </c>
       <c r="D25" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="33">
         <v>1</v>
@@ -2043,27 +2039,27 @@
         <v>46474</v>
       </c>
       <c r="I25" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K25" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>61</v>
-      </c>
       <c r="D26" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="33">
         <v>2</v>
@@ -2080,27 +2076,27 @@
         <v>46415</v>
       </c>
       <c r="I26" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>64</v>
-      </c>
       <c r="D27" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="33">
         <v>3</v>
@@ -2117,25 +2113,25 @@
         <v>46535</v>
       </c>
       <c r="I27" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J27" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K27" s="30"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>66</v>
-      </c>
       <c r="D28" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" s="33">
         <v>5</v>
@@ -2152,27 +2148,27 @@
         <v>46535</v>
       </c>
       <c r="I28" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K28" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>69</v>
-      </c>
       <c r="D29" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" s="33">
         <v>4</v>
@@ -2189,27 +2185,27 @@
         <v>46415</v>
       </c>
       <c r="I29" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="30" t="s">
         <v>70</v>
-      </c>
-      <c r="J29" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" s="30" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A30" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>73</v>
-      </c>
       <c r="D30" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="33">
         <v>6</v>
@@ -2226,27 +2222,27 @@
         <v>46535</v>
       </c>
       <c r="I30" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K30" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>76</v>
-      </c>
       <c r="D31" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" s="33">
         <v>8</v>
@@ -2263,27 +2259,27 @@
         <v>46535</v>
       </c>
       <c r="I31" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>79</v>
-      </c>
       <c r="D32" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="33">
         <v>8</v>
@@ -2300,25 +2296,25 @@
         <v>46535</v>
       </c>
       <c r="I32" s="35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K32" s="30"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>82</v>
-      </c>
       <c r="D33" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" s="33">
         <v>8</v>
@@ -2335,27 +2331,27 @@
         <v>46566</v>
       </c>
       <c r="I33" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K33" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>85</v>
-      </c>
       <c r="D34" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E34" s="33">
         <v>9</v>
@@ -2372,27 +2368,27 @@
         <v>46566</v>
       </c>
       <c r="I34" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K34" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>88</v>
-      </c>
       <c r="D35" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" s="33">
         <v>9</v>
@@ -2409,27 +2405,27 @@
         <v>46658</v>
       </c>
       <c r="I35" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="J35" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="30" t="s">
         <v>89</v>
-      </c>
-      <c r="J35" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>92</v>
-      </c>
       <c r="D36" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" s="33">
         <v>1</v>
@@ -2446,27 +2442,27 @@
         <v>46566</v>
       </c>
       <c r="I36" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J36" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K36" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="C37" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="31" t="s">
-        <v>96</v>
-      </c>
       <c r="D37" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" s="33">
         <v>12</v>
@@ -2483,27 +2479,27 @@
         <v>46658</v>
       </c>
       <c r="I37" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J37" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="30" t="s">
         <v>97</v>
-      </c>
-      <c r="J37" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" s="30" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>100</v>
-      </c>
       <c r="D38" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E38" s="33">
         <v>9</v>
@@ -2520,25 +2516,25 @@
         <v>46840</v>
       </c>
       <c r="I38" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J38" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K38" s="30"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>102</v>
-      </c>
       <c r="D39" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E39" s="33">
         <v>10</v>
@@ -2555,27 +2551,27 @@
         <v>46780</v>
       </c>
       <c r="I39" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>105</v>
-      </c>
       <c r="D40" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40" s="33">
         <v>16</v>
@@ -2592,25 +2588,25 @@
         <v>47024</v>
       </c>
       <c r="I40" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J40" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K40" s="30"/>
     </row>
     <row r="41" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="B41" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>107</v>
-      </c>
       <c r="D41" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" s="33">
         <v>15</v>
@@ -2627,27 +2623,27 @@
         <v>46901</v>
       </c>
       <c r="I41" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K41" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="B42" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>110</v>
-      </c>
       <c r="D42" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E42" s="33">
         <v>18</v>
@@ -2664,25 +2660,25 @@
         <v>47085</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K42" s="30"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B43" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" s="31" t="s">
-        <v>112</v>
-      </c>
       <c r="D43" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E43" s="33">
         <v>24</v>
@@ -2699,27 +2695,27 @@
         <v>47024</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K43" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="C44" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="30" t="s">
-        <v>116</v>
-      </c>
       <c r="D44" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E44" s="33">
         <v>18</v>
@@ -2736,25 +2732,25 @@
         <v>46871</v>
       </c>
       <c r="I44" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J44" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K44" s="30"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>118</v>
-      </c>
       <c r="D45" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E45" s="33">
         <v>19</v>
@@ -2771,25 +2767,25 @@
         <v>47024</v>
       </c>
       <c r="I45" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J45" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K45" s="30"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B46" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>120</v>
-      </c>
       <c r="D46" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="33">
         <v>24</v>
@@ -2806,25 +2802,25 @@
         <v>47205</v>
       </c>
       <c r="I46" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J46" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K46" s="30"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>122</v>
-      </c>
       <c r="D47" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="33">
         <v>28</v>
@@ -2841,25 +2837,25 @@
         <v>47236</v>
       </c>
       <c r="I47" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J47" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K47" s="30"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>124</v>
-      </c>
       <c r="D48" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48" s="33">
         <v>30</v>
@@ -2876,27 +2872,27 @@
         <v>47205</v>
       </c>
       <c r="I48" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K48" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>127</v>
-      </c>
       <c r="D49" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E49" s="33">
         <v>31</v>
@@ -2913,27 +2909,27 @@
         <v>47236</v>
       </c>
       <c r="I49" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K49" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>130</v>
-      </c>
       <c r="D50" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E50" s="33">
         <v>32</v>
@@ -2950,25 +2946,25 @@
         <v>47327</v>
       </c>
       <c r="I50" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J50" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K50" s="30"/>
     </row>
     <row r="51" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A51" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>132</v>
-      </c>
       <c r="D51" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E51" s="33">
         <v>34</v>
@@ -2985,27 +2981,27 @@
         <v>47327</v>
       </c>
       <c r="I51" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J51" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K51" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B52" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>135</v>
-      </c>
       <c r="D52" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52" s="33">
         <v>34</v>
@@ -3022,27 +3018,27 @@
         <v>47327</v>
       </c>
       <c r="I52" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J52" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="B53" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>137</v>
-      </c>
       <c r="D53" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="33">
         <v>35</v>
@@ -3059,25 +3055,25 @@
         <v>47358</v>
       </c>
       <c r="I53" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K53" s="30"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="B54" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>139</v>
-      </c>
       <c r="D54" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="33">
         <v>35</v>
@@ -3094,25 +3090,25 @@
         <v>47389</v>
       </c>
       <c r="I54" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="33" t="s">
         <v>24</v>
-      </c>
-      <c r="J54" s="33" t="s">
-        <v>25</v>
       </c>
       <c r="K54" s="30"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B55" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>141</v>
-      </c>
       <c r="D55" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E55" s="33">
         <v>36</v>
@@ -3129,27 +3125,27 @@
         <v>47389</v>
       </c>
       <c r="I55" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J55" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K55" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A56" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B56" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="38" t="s">
+      <c r="C56" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="C56" s="30" t="s">
-        <v>145</v>
-      </c>
       <c r="D56" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" s="33">
         <v>37</v>
@@ -3166,27 +3162,27 @@
         <v>47570</v>
       </c>
       <c r="I56" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="30" t="s">
         <v>146</v>
-      </c>
-      <c r="J56" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K56" s="30" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>149</v>
-      </c>
       <c r="D57" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E57" s="33">
         <v>42</v>
@@ -3203,13 +3199,13 @@
         <v>47570</v>
       </c>
       <c r="I57" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="30" t="s">
         <v>150</v>
-      </c>
-      <c r="J57" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K57" s="30" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.4">
@@ -3283,12 +3279,12 @@
   <sheetData>
     <row r="1" spans="1:48" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.4">
       <c r="G3" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -3302,7 +3298,7 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T3" s="10"/>
       <c r="U3" s="10"/>
@@ -3316,7 +3312,7 @@
       <c r="AC3" s="10"/>
       <c r="AD3" s="10"/>
       <c r="AE3" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF3" s="12"/>
       <c r="AG3" s="12"/>
@@ -3330,7 +3326,7 @@
       <c r="AO3" s="12"/>
       <c r="AP3" s="12"/>
       <c r="AQ3" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AR3" s="14"/>
       <c r="AS3" s="14"/>
@@ -3340,22 +3336,22 @@
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="C4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="D4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="F4" s="15" t="s">
         <v>14</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>15</v>
       </c>
       <c r="G4" s="16">
         <v>1</v>
@@ -12235,287 +12231,287 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>160</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/PhD_Timeline_ANU.xlsx
+++ b/PhD_Timeline_ANU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u8363323_anu_edu_au/Documents/Doctoral Documents/PhD-Timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D83AFB-567E-4A2F-A9A9-8A8689857293}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE162E10-9FDD-4263-8F29-62575E5C33A4}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1205,6 +1205,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1414,7 +1418,7 @@
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
       <c r="D3" s="36">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="23"/>
@@ -1432,7 +1436,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="25">
         <f>H24</f>
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
@@ -1450,7 +1454,7 @@
       <c r="C5" s="23"/>
       <c r="D5" s="25">
         <f>H34</f>
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
@@ -1468,7 +1472,7 @@
       <c r="C6" s="23"/>
       <c r="D6" s="25">
         <f>H48</f>
-        <v>47205</v>
+        <v>47206</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="23"/>
@@ -1486,7 +1490,7 @@
       <c r="C7" s="23"/>
       <c r="D7" s="26">
         <f>H55</f>
-        <v>47389</v>
+        <v>47390</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
@@ -1504,7 +1508,7 @@
       <c r="C8" s="23"/>
       <c r="D8" s="25">
         <f>EDATE($D$3,48)-1</f>
-        <v>47754</v>
+        <v>47755</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -1522,7 +1526,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="25">
         <f>EDATE($D$3,48)-1</f>
-        <v>47754</v>
+        <v>47755</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -1540,7 +1544,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="25">
         <f>EDATE($D$3,60)-1</f>
-        <v>48119</v>
+        <v>48120</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
@@ -1558,7 +1562,7 @@
       <c r="C11" s="23"/>
       <c r="D11" s="27">
         <f>COUNTIF(J14:J57,"Done")/COUNTA(A14:A57)</f>
-        <v>4.5454545454545456E-2</v>
+        <v>6.8181818181818177E-2</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
@@ -1637,17 +1641,17 @@
       </c>
       <c r="G14" s="34">
         <f t="shared" ref="G14:G57" si="0">EDATE($D$3,E14-1)</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H14" s="34">
         <f t="shared" ref="H14:H57" si="1">EDATE($D$3,F14)-1</f>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K14" s="30" t="s">
         <v>25</v>
@@ -1674,11 +1678,11 @@
       </c>
       <c r="G15" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H15" s="34">
         <f t="shared" si="1"/>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I15" s="35" t="s">
         <v>23</v>
@@ -1709,11 +1713,11 @@
       </c>
       <c r="G16" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H16" s="34">
         <f t="shared" si="1"/>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I16" s="35" t="s">
         <v>23</v>
@@ -1744,11 +1748,11 @@
       </c>
       <c r="G17" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H17" s="34">
         <f t="shared" si="1"/>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I17" s="35" t="s">
         <v>23</v>
@@ -1779,11 +1783,11 @@
       </c>
       <c r="G18" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H18" s="34">
         <f t="shared" si="1"/>
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="I18" s="35" t="s">
         <v>23</v>
@@ -1814,17 +1818,17 @@
       </c>
       <c r="G19" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H19" s="34">
         <f t="shared" si="1"/>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I19" s="35" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K19" s="30"/>
     </row>
@@ -1849,11 +1853,11 @@
       </c>
       <c r="G20" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H20" s="34">
         <f t="shared" si="1"/>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I20" s="35" t="s">
         <v>39</v>
@@ -1884,11 +1888,11 @@
       </c>
       <c r="G21" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H21" s="34">
         <f t="shared" si="1"/>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="I21" s="35" t="s">
         <v>39</v>
@@ -1921,11 +1925,11 @@
       </c>
       <c r="G22" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H22" s="34">
         <f t="shared" si="1"/>
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="I22" s="35" t="s">
         <v>39</v>
@@ -1958,11 +1962,11 @@
       </c>
       <c r="G23" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H23" s="34">
         <f t="shared" si="1"/>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="I23" s="35" t="s">
         <v>23</v>
@@ -1995,11 +1999,11 @@
       </c>
       <c r="G24" s="34">
         <f t="shared" si="0"/>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="H24" s="34">
         <f t="shared" si="1"/>
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="I24" s="35" t="s">
         <v>39</v>
@@ -2032,11 +2036,11 @@
       </c>
       <c r="G25" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H25" s="34">
         <f t="shared" si="1"/>
-        <v>46474</v>
+        <v>46475</v>
       </c>
       <c r="I25" s="35" t="s">
         <v>23</v>
@@ -2069,11 +2073,11 @@
       </c>
       <c r="G26" s="34">
         <f t="shared" si="0"/>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="H26" s="34">
         <f t="shared" si="1"/>
-        <v>46415</v>
+        <v>46416</v>
       </c>
       <c r="I26" s="35" t="s">
         <v>39</v>
@@ -2106,11 +2110,11 @@
       </c>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="H27" s="34">
         <f t="shared" si="1"/>
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="I27" s="35" t="s">
         <v>23</v>
@@ -2141,11 +2145,11 @@
       </c>
       <c r="G28" s="34">
         <f t="shared" si="0"/>
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="H28" s="34">
         <f t="shared" si="1"/>
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="I28" s="35" t="s">
         <v>23</v>
@@ -2178,11 +2182,11 @@
       </c>
       <c r="G29" s="34">
         <f t="shared" si="0"/>
-        <v>46385</v>
+        <v>46386</v>
       </c>
       <c r="H29" s="34">
         <f t="shared" si="1"/>
-        <v>46415</v>
+        <v>46416</v>
       </c>
       <c r="I29" s="35" t="s">
         <v>69</v>
@@ -2219,7 +2223,7 @@
       </c>
       <c r="H30" s="34">
         <f t="shared" si="1"/>
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="I30" s="35" t="s">
         <v>23</v>
@@ -2252,11 +2256,11 @@
       </c>
       <c r="G31" s="34">
         <f t="shared" si="0"/>
-        <v>46506</v>
+        <v>46507</v>
       </c>
       <c r="H31" s="34">
         <f t="shared" si="1"/>
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="I31" s="35" t="s">
         <v>39</v>
@@ -2289,11 +2293,11 @@
       </c>
       <c r="G32" s="34">
         <f t="shared" si="0"/>
-        <v>46506</v>
+        <v>46507</v>
       </c>
       <c r="H32" s="34">
         <f t="shared" si="1"/>
-        <v>46535</v>
+        <v>46536</v>
       </c>
       <c r="I32" s="35" t="s">
         <v>79</v>
@@ -2324,11 +2328,11 @@
       </c>
       <c r="G33" s="34">
         <f t="shared" si="0"/>
-        <v>46506</v>
+        <v>46507</v>
       </c>
       <c r="H33" s="34">
         <f t="shared" si="1"/>
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="I33" s="35" t="s">
         <v>23</v>
@@ -2361,11 +2365,11 @@
       </c>
       <c r="G34" s="34">
         <f t="shared" si="0"/>
-        <v>46536</v>
+        <v>46537</v>
       </c>
       <c r="H34" s="34">
         <f t="shared" si="1"/>
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="I34" s="35" t="s">
         <v>23</v>
@@ -2398,11 +2402,11 @@
       </c>
       <c r="G35" s="34">
         <f t="shared" si="0"/>
-        <v>46536</v>
+        <v>46537</v>
       </c>
       <c r="H35" s="34">
         <f t="shared" si="1"/>
-        <v>46658</v>
+        <v>46659</v>
       </c>
       <c r="I35" s="35" t="s">
         <v>88</v>
@@ -2435,11 +2439,11 @@
       </c>
       <c r="G36" s="34">
         <f t="shared" si="0"/>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H36" s="34">
         <f t="shared" si="1"/>
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="I36" s="35" t="s">
         <v>23</v>
@@ -2472,11 +2476,11 @@
       </c>
       <c r="G37" s="34">
         <f t="shared" si="0"/>
-        <v>46628</v>
+        <v>46629</v>
       </c>
       <c r="H37" s="34">
         <f t="shared" si="1"/>
-        <v>46658</v>
+        <v>46659</v>
       </c>
       <c r="I37" s="35" t="s">
         <v>96</v>
@@ -2509,11 +2513,11 @@
       </c>
       <c r="G38" s="34">
         <f t="shared" si="0"/>
-        <v>46536</v>
+        <v>46537</v>
       </c>
       <c r="H38" s="34">
         <f t="shared" si="1"/>
-        <v>46840</v>
+        <v>46841</v>
       </c>
       <c r="I38" s="35" t="s">
         <v>23</v>
@@ -2544,11 +2548,11 @@
       </c>
       <c r="G39" s="34">
         <f t="shared" si="0"/>
-        <v>46567</v>
+        <v>46568</v>
       </c>
       <c r="H39" s="34">
         <f t="shared" si="1"/>
-        <v>46780</v>
+        <v>46781</v>
       </c>
       <c r="I39" s="35" t="s">
         <v>39</v>
@@ -2581,11 +2585,11 @@
       </c>
       <c r="G40" s="34">
         <f t="shared" si="0"/>
-        <v>46750</v>
+        <v>46751</v>
       </c>
       <c r="H40" s="34">
         <f t="shared" si="1"/>
-        <v>47024</v>
+        <v>47025</v>
       </c>
       <c r="I40" s="35" t="s">
         <v>23</v>
@@ -2616,11 +2620,11 @@
       </c>
       <c r="G41" s="34">
         <f t="shared" si="0"/>
-        <v>46720</v>
+        <v>46721</v>
       </c>
       <c r="H41" s="34">
         <f t="shared" si="1"/>
-        <v>46901</v>
+        <v>46902</v>
       </c>
       <c r="I41" s="35" t="s">
         <v>23</v>
@@ -2657,7 +2661,7 @@
       </c>
       <c r="H42" s="34">
         <f t="shared" si="1"/>
-        <v>47085</v>
+        <v>47086</v>
       </c>
       <c r="I42" s="35" t="s">
         <v>39</v>
@@ -2688,11 +2692,11 @@
       </c>
       <c r="G43" s="34">
         <f t="shared" si="0"/>
-        <v>46994</v>
+        <v>46995</v>
       </c>
       <c r="H43" s="34">
         <f t="shared" si="1"/>
-        <v>47024</v>
+        <v>47025</v>
       </c>
       <c r="I43" s="35" t="s">
         <v>96</v>
@@ -2729,7 +2733,7 @@
       </c>
       <c r="H44" s="34">
         <f t="shared" si="1"/>
-        <v>46871</v>
+        <v>46872</v>
       </c>
       <c r="I44" s="35" t="s">
         <v>39</v>
@@ -2760,11 +2764,11 @@
       </c>
       <c r="G45" s="34">
         <f t="shared" si="0"/>
-        <v>46841</v>
+        <v>46842</v>
       </c>
       <c r="H45" s="34">
         <f t="shared" si="1"/>
-        <v>47024</v>
+        <v>47025</v>
       </c>
       <c r="I45" s="35" t="s">
         <v>23</v>
@@ -2795,11 +2799,11 @@
       </c>
       <c r="G46" s="34">
         <f t="shared" si="0"/>
-        <v>46994</v>
+        <v>46995</v>
       </c>
       <c r="H46" s="34">
         <f t="shared" si="1"/>
-        <v>47205</v>
+        <v>47206</v>
       </c>
       <c r="I46" s="35" t="s">
         <v>23</v>
@@ -2830,11 +2834,11 @@
       </c>
       <c r="G47" s="34">
         <f t="shared" si="0"/>
-        <v>47116</v>
+        <v>47117</v>
       </c>
       <c r="H47" s="34">
         <f t="shared" si="1"/>
-        <v>47236</v>
+        <v>47237</v>
       </c>
       <c r="I47" s="35" t="s">
         <v>23</v>
@@ -2869,7 +2873,7 @@
       </c>
       <c r="H48" s="34">
         <f t="shared" si="1"/>
-        <v>47205</v>
+        <v>47206</v>
       </c>
       <c r="I48" s="35" t="s">
         <v>23</v>
@@ -2902,11 +2906,11 @@
       </c>
       <c r="G49" s="34">
         <f t="shared" si="0"/>
-        <v>47206</v>
+        <v>47207</v>
       </c>
       <c r="H49" s="34">
         <f t="shared" si="1"/>
-        <v>47236</v>
+        <v>47237</v>
       </c>
       <c r="I49" s="35" t="s">
         <v>23</v>
@@ -2939,11 +2943,11 @@
       </c>
       <c r="G50" s="34">
         <f t="shared" si="0"/>
-        <v>47237</v>
+        <v>47238</v>
       </c>
       <c r="H50" s="34">
         <f t="shared" si="1"/>
-        <v>47327</v>
+        <v>47328</v>
       </c>
       <c r="I50" s="35" t="s">
         <v>39</v>
@@ -2974,11 +2978,11 @@
       </c>
       <c r="G51" s="34">
         <f t="shared" si="0"/>
-        <v>47298</v>
+        <v>47299</v>
       </c>
       <c r="H51" s="34">
         <f t="shared" si="1"/>
-        <v>47327</v>
+        <v>47328</v>
       </c>
       <c r="I51" s="35" t="s">
         <v>23</v>
@@ -3011,11 +3015,11 @@
       </c>
       <c r="G52" s="34">
         <f t="shared" si="0"/>
-        <v>47298</v>
+        <v>47299</v>
       </c>
       <c r="H52" s="34">
         <f t="shared" si="1"/>
-        <v>47327</v>
+        <v>47328</v>
       </c>
       <c r="I52" s="35" t="s">
         <v>39</v>
@@ -3048,11 +3052,11 @@
       </c>
       <c r="G53" s="34">
         <f t="shared" si="0"/>
-        <v>47328</v>
+        <v>47329</v>
       </c>
       <c r="H53" s="34">
         <f t="shared" si="1"/>
-        <v>47358</v>
+        <v>47359</v>
       </c>
       <c r="I53" s="35" t="s">
         <v>39</v>
@@ -3083,11 +3087,11 @@
       </c>
       <c r="G54" s="34">
         <f t="shared" si="0"/>
-        <v>47328</v>
+        <v>47329</v>
       </c>
       <c r="H54" s="34">
         <f t="shared" si="1"/>
-        <v>47389</v>
+        <v>47390</v>
       </c>
       <c r="I54" s="35" t="s">
         <v>23</v>
@@ -3118,11 +3122,11 @@
       </c>
       <c r="G55" s="34">
         <f t="shared" si="0"/>
-        <v>47359</v>
+        <v>47360</v>
       </c>
       <c r="H55" s="34">
         <f t="shared" si="1"/>
-        <v>47389</v>
+        <v>47390</v>
       </c>
       <c r="I55" s="35" t="s">
         <v>23</v>
@@ -3155,11 +3159,11 @@
       </c>
       <c r="G56" s="34">
         <f t="shared" si="0"/>
-        <v>47390</v>
+        <v>47391</v>
       </c>
       <c r="H56" s="34">
         <f t="shared" si="1"/>
-        <v>47570</v>
+        <v>47571</v>
       </c>
       <c r="I56" s="35" t="s">
         <v>145</v>
@@ -3196,7 +3200,7 @@
       </c>
       <c r="H57" s="34">
         <f t="shared" si="1"/>
-        <v>47570</v>
+        <v>47571</v>
       </c>
       <c r="I57" s="35" t="s">
         <v>149</v>

--- a/PhD_Timeline_ANU.xlsx
+++ b/PhD_Timeline_ANU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u8363323_anu_edu_au/Documents/Doctoral Documents/PhD-Timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE162E10-9FDD-4263-8F29-62575E5C33A4}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3119A1E6-1864-4E5E-A221-9081AE688B1F}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timeline" sheetId="1" r:id="rId1"/>
@@ -1205,10 +1205,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2046,7 +2042,7 @@
         <v>23</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K25" s="30" t="s">
         <v>58</v>

--- a/PhD_Timeline_ANU.xlsx
+++ b/PhD_Timeline_ANU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u8363323_anu_edu_au/Documents/Doctoral Documents/PhD-Timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3119A1E6-1864-4E5E-A221-9081AE688B1F}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="11_0EC2900A77C21E90B6F1C8A2499E150DCEDE6822" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30AFA41D-D0AD-48CB-B89A-0996F71746A1}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timeline" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="231">
   <si>
     <t>Yehezkiel's PhD Timeline - ANU RSES (3-year plan)</t>
   </si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>Agree expectations with supervisor: feedback turnaround, hours (40 h/wk), WFH vs on-campus, etc</t>
-  </si>
-  <si>
-    <t>Delayed</t>
   </si>
   <si>
     <t>Common source of misunderstanding - settle early and in writing</t>
@@ -1498,7 +1495,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -1719,7 +1716,7 @@
         <v>23</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K16" s="30"/>
     </row>
@@ -1824,7 +1821,7 @@
         <v>23</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K19" s="30"/>
     </row>
@@ -1894,21 +1891,21 @@
         <v>39</v>
       </c>
       <c r="J21" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="30" t="s">
         <v>42</v>
-      </c>
-      <c r="K21" s="30" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>11</v>
@@ -1934,18 +1931,18 @@
         <v>24</v>
       </c>
       <c r="K22" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>11</v>
@@ -1968,24 +1965,24 @@
         <v>23</v>
       </c>
       <c r="J23" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="30" t="s">
         <v>49</v>
-      </c>
-      <c r="K23" s="30" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>52</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>53</v>
       </c>
       <c r="E24" s="33">
         <v>3</v>
@@ -2008,18 +2005,18 @@
         <v>24</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="C25" s="30" t="s">
         <v>56</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>57</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>11</v>
@@ -2045,18 +2042,18 @@
         <v>30</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>60</v>
       </c>
       <c r="D26" s="29" t="s">
         <v>11</v>
@@ -2082,18 +2079,18 @@
         <v>24</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="30" t="s">
         <v>62</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>63</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>11</v>
@@ -2122,13 +2119,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>64</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>65</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>11</v>
@@ -2154,21 +2151,21 @@
         <v>24</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>68</v>
-      </c>
       <c r="D29" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" s="33">
         <v>4</v>
@@ -2185,24 +2182,24 @@
         <v>46416</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J29" s="33" t="s">
         <v>24</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A30" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="30" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>72</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>11</v>
@@ -2228,21 +2225,21 @@
         <v>24</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>75</v>
-      </c>
       <c r="D31" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="33">
         <v>8</v>
@@ -2265,21 +2262,21 @@
         <v>24</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>78</v>
-      </c>
       <c r="D32" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" s="33">
         <v>8</v>
@@ -2296,7 +2293,7 @@
         <v>46536</v>
       </c>
       <c r="I32" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J32" s="33" t="s">
         <v>24</v>
@@ -2305,13 +2302,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="30" t="s">
         <v>80</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>81</v>
       </c>
       <c r="D33" s="29" t="s">
         <v>11</v>
@@ -2337,21 +2334,21 @@
         <v>24</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>84</v>
-      </c>
       <c r="D34" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E34" s="33">
         <v>9</v>
@@ -2374,18 +2371,18 @@
         <v>24</v>
       </c>
       <c r="K34" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="30" t="s">
         <v>86</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>87</v>
       </c>
       <c r="D35" s="29" t="s">
         <v>11</v>
@@ -2405,24 +2402,24 @@
         <v>46659</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J35" s="33" t="s">
         <v>24</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="30" t="s">
         <v>90</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>91</v>
       </c>
       <c r="D36" s="29" t="s">
         <v>11</v>
@@ -2448,21 +2445,21 @@
         <v>24</v>
       </c>
       <c r="K36" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="C37" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="31" t="s">
-        <v>95</v>
-      </c>
       <c r="D37" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E37" s="33">
         <v>12</v>
@@ -2479,24 +2476,24 @@
         <v>46659</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J37" s="33" t="s">
         <v>24</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="30" t="s">
         <v>98</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>99</v>
       </c>
       <c r="D38" s="29" t="s">
         <v>11</v>
@@ -2525,13 +2522,13 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="30" t="s">
         <v>100</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>101</v>
       </c>
       <c r="D39" s="29" t="s">
         <v>11</v>
@@ -2557,18 +2554,18 @@
         <v>24</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="30" t="s">
         <v>103</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>104</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>11</v>
@@ -2597,13 +2594,13 @@
     </row>
     <row r="41" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>105</v>
-      </c>
-      <c r="B41" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>106</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>11</v>
@@ -2629,18 +2626,18 @@
         <v>24</v>
       </c>
       <c r="K41" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>108</v>
-      </c>
-      <c r="B42" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>109</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>11</v>
@@ -2669,16 +2666,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="B43" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="31" t="s">
-        <v>111</v>
-      </c>
       <c r="D43" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E43" s="33">
         <v>24</v>
@@ -2695,24 +2692,24 @@
         <v>47025</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J43" s="33" t="s">
         <v>24</v>
       </c>
       <c r="K43" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="C44" s="30" t="s">
         <v>114</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>115</v>
       </c>
       <c r="D44" s="29" t="s">
         <v>11</v>
@@ -2741,13 +2738,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="30" t="s">
         <v>116</v>
-      </c>
-      <c r="B45" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>117</v>
       </c>
       <c r="D45" s="29" t="s">
         <v>11</v>
@@ -2776,13 +2773,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="30" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>119</v>
       </c>
       <c r="D46" s="29" t="s">
         <v>11</v>
@@ -2811,13 +2808,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="30" t="s">
         <v>120</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>121</v>
       </c>
       <c r="D47" s="29" t="s">
         <v>11</v>
@@ -2846,16 +2843,16 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B48" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>123</v>
-      </c>
       <c r="D48" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E48" s="33">
         <v>30</v>
@@ -2878,21 +2875,21 @@
         <v>24</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>126</v>
-      </c>
       <c r="D49" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E49" s="33">
         <v>31</v>
@@ -2915,18 +2912,18 @@
         <v>24</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="30" t="s">
         <v>128</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>129</v>
       </c>
       <c r="D50" s="29" t="s">
         <v>11</v>
@@ -2955,16 +2952,16 @@
     </row>
     <row r="51" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A51" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B51" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>131</v>
-      </c>
       <c r="D51" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E51" s="33">
         <v>34</v>
@@ -2987,21 +2984,21 @@
         <v>24</v>
       </c>
       <c r="K51" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="B52" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>134</v>
-      </c>
       <c r="D52" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E52" s="33">
         <v>34</v>
@@ -3024,18 +3021,18 @@
         <v>24</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="30" t="s">
         <v>135</v>
-      </c>
-      <c r="B53" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>136</v>
       </c>
       <c r="D53" s="29" t="s">
         <v>11</v>
@@ -3064,13 +3061,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="30" t="s">
         <v>137</v>
-      </c>
-      <c r="B54" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>138</v>
       </c>
       <c r="D54" s="29" t="s">
         <v>11</v>
@@ -3099,16 +3096,16 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B55" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>140</v>
-      </c>
       <c r="D55" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E55" s="33">
         <v>36</v>
@@ -3131,18 +3128,18 @@
         <v>24</v>
       </c>
       <c r="K55" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A56" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="B56" s="38" t="s">
+      <c r="C56" s="30" t="s">
         <v>143</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>144</v>
       </c>
       <c r="D56" s="29" t="s">
         <v>11</v>
@@ -3162,27 +3159,27 @@
         <v>47571</v>
       </c>
       <c r="I56" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J56" s="33" t="s">
         <v>24</v>
       </c>
       <c r="K56" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C57" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>148</v>
-      </c>
       <c r="D57" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E57" s="33">
         <v>42</v>
@@ -3199,13 +3196,13 @@
         <v>47571</v>
       </c>
       <c r="I57" s="35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J57" s="33" t="s">
         <v>24</v>
       </c>
       <c r="K57" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.4">
@@ -3279,12 +3276,12 @@
   <sheetData>
     <row r="1" spans="1:48" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.4">
       <c r="G3" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -3298,7 +3295,7 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T3" s="10"/>
       <c r="U3" s="10"/>
@@ -3312,7 +3309,7 @@
       <c r="AC3" s="10"/>
       <c r="AD3" s="10"/>
       <c r="AE3" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AF3" s="12"/>
       <c r="AG3" s="12"/>
@@ -3326,7 +3323,7 @@
       <c r="AO3" s="12"/>
       <c r="AP3" s="12"/>
       <c r="AQ3" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AR3" s="14"/>
       <c r="AS3" s="14"/>
@@ -12231,287 +12228,287 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.75" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="37.299999999999997" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
